--- a/StructureDefinition-ncpi-maf.xlsx
+++ b/StructureDefinition-ncpi-maf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -374,7 +374,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -534,7 +534,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -563,7 +563,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -646,7 +646,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -680,7 +680,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -704,7 +704,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Location|4.0.1)
 </t>
   </si>
   <si>
@@ -735,7 +735,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -758,7 +758,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -849,7 +849,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -931,7 +931,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -963,7 +963,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1019,7 +1019,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1052,7 +1052,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1064,7 +1064,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1092,7 +1092,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1197,7 +1197,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1247,7 +1247,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1280,7 +1280,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1317,7 +1317,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1339,7 +1339,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -2188,7 +2188,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.26171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-ncpi-maf.xlsx
+++ b/StructureDefinition-ncpi-maf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-ncpi-maf.xlsx
+++ b/StructureDefinition-ncpi-maf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-maf.xlsx
+++ b/StructureDefinition-ncpi-maf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-maf.xlsx
+++ b/StructureDefinition-ncpi-maf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
